--- a/library_software/library_management.xlsx
+++ b/library_software/library_management.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codeplay\daily_cyber\library_software\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1D588D-39C6-4475-A3A6-3BDC7A0EC68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E651F5C-60A4-4F2A-A5DD-D6942B580ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Users" sheetId="1" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" r:id="rId1"/>
     <sheet name="Login" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/activeX/activeX1.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D7053240-CE69-11CD-A777-00DD01143C57}" ax:persistence="persistStreamInit" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{8BD21D10-EC42-11CE-9E0D-00AA006002F3}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/activeX/activeX2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/activeX/activeX3.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{8BD21D10-EC42-11CE-9E0D-00AA006002F3}" ax:persistence="persistStreamInit" r:id="rId1"/>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D7053240-CE69-11CD-A777-00DD01143C57}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -611,27 +611,27 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="2052" r:id="rId3" name="CommandButton1">
+        <control shapeId="2050" r:id="rId3" name="TextBox1">
           <controlPr defaultSize="0" autoLine="0" r:id="rId4">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>419100</xdr:colOff>
-                <xdr:row>9</xdr:row>
-                <xdr:rowOff>127000</xdr:rowOff>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>590550</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>19050</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>273050</xdr:colOff>
-                <xdr:row>11</xdr:row>
-                <xdr:rowOff>177800</xdr:rowOff>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>50800</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>50800</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="2052" r:id="rId3" name="CommandButton1"/>
+        <control shapeId="2050" r:id="rId3" name="TextBox1"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -661,27 +661,27 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="2050" r:id="rId7" name="TextBox1">
+        <control shapeId="2052" r:id="rId7" name="CommandButton1">
           <controlPr defaultSize="0" autoLine="0" r:id="rId8">
             <anchor moveWithCells="1">
               <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>590550</xdr:colOff>
-                <xdr:row>5</xdr:row>
-                <xdr:rowOff>19050</xdr:rowOff>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>419100</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>127000</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>50800</xdr:colOff>
-                <xdr:row>6</xdr:row>
-                <xdr:rowOff>50800</xdr:rowOff>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>273050</xdr:colOff>
+                <xdr:row>11</xdr:row>
+                <xdr:rowOff>177800</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="2050" r:id="rId7" name="TextBox1"/>
+        <control shapeId="2052" r:id="rId7" name="CommandButton1"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
